--- a/output/pdf_financials_xlsx/REKO.xlsx
+++ b/output/pdf_financials_xlsx/REKO.xlsx
@@ -2014,28 +2014,28 @@
         <v>1.589</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.005225</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.00474</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.006565</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.005448</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.004441</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.006209</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.014023</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.012139</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2104,28 +2104,28 @@
         <v>1.589</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.005225</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.00474</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.006565</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.005448</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.005</v>
+        <v>0.009441</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.010709</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.014023</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.012139</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.014906</v>
+        <v>0.000883</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.013468</v>
+        <v>0.001329</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">

--- a/output/pdf_financials_xlsx/REKO.xlsx
+++ b/output/pdf_financials_xlsx/REKO.xlsx
@@ -3565,10 +3565,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>2.493</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>2.013</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -3577,27 +3577,25 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.001396</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.001651</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.001977</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.001766</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.00397</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002167</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>0.003691</v>
       </c>
     </row>
     <row r="68">
@@ -3639,10 +3637,8 @@
       <c r="L68" s="3" t="n">
         <v>0.004163</v>
       </c>
-      <c r="M68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M68" s="3" t="n">
+        <v>0.003691</v>
       </c>
     </row>
     <row r="69">
@@ -5420,13 +5416,13 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
@@ -19646,7 +19642,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -19868,7 +19868,11 @@
           <t>Stock option expense (Note 14)</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -20850,7 +20854,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E187" s="5" t="n">
         <v>0.199</v>
       </c>
@@ -20998,7 +21006,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E189" s="5" t="n">
         <v>0.083</v>
       </c>
@@ -21220,7 +21232,11 @@
           <t>Stock option expense (Note 12)</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E192" s="5" t="n">
         <v>0.022</v>
       </c>
